--- a/m365-copilot-agent/knowledge/backlog_template.xlsx
+++ b/m365-copilot-agent/knowledge/backlog_template.xlsx
@@ -7,11 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Epics" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Features" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Stories" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Traceability" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Open Questions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Case-Type Matrix" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Interface Inventory" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Epics" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Features" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Stories" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Traceability" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Open Questions" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -438,6 +440,244 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Case Type</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Parent Case Type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Trigger/Entry Point</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Primary Actor</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Key Stages</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Special Handling Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="45" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>EX-CT1 Claim</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Policyholder submits claim via web portal</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Policyholder</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Intake &gt; Triage &gt; Adjuster Review &gt; Determination &gt; Payment/Close</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Supports Withdraw and Hold; Skip only from Triage when auto-approved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="45" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>EX-CT2 Assistance Request</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>EX-CT1 Claim</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Adjuster requests specialist review mid-claim</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Adjuster</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Requested &gt; In Review &gt; Resolved</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Blocks parent claim's Determination stage until resolved (dependency gating).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Interface ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Source System</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Target System</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Protocol</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Interchange/Message Count</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Data Objects Exchanged</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Error Handling Approach</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>System of Record</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="45" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>EX-IF1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Claims Platform</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Policy Admin System</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>2 (policy lookup, coverage lookup)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Policy, Coverage, Named Insured</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Synchronous call; 3x retry with exponential backoff; manual work-queue routing on final failure</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Policy Admin System</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="D2:D200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Inbound,Outbound,Bidirectional"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -526,7 +766,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -620,13 +860,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -634,20 +874,23 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="36" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="24" customWidth="1" min="16" max="16"/>
-    <col width="26" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="34" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -678,76 +921,91 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Summary (As-a/I-want/so-that)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Sizing Drivers</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Dependencies</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Story Size</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Complexity</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Design Details</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Actor/Persona</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Labels/Components</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Requirement Origin</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Source Reference</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Assumptions</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Out of Scope</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="90" customHeight="1">
+    <row r="2" ht="100" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>EX-ST1</t>
@@ -775,89 +1033,110 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>As a policyholder, I want to upload photos and documents for my claim, so that the adjuster has what they need without a follow-up call.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>During claim submission, the user can attach one or more files (photo, PDF) as supporting evidence before final submission.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Given a claim in progress, When the user selects up to 10 files under 25MB each, Then the files upload and appear in a document list.
 Given a file exceeds 25MB, When the user attempts to upload it, Then an inline error explains the size limit and the file is rejected.</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>1 screen (upload panel), 2 validation rules (file count, file size), 0 integrations, 2 exception paths (oversize file, virus-scan failure)</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>EX-ST0 (Start new claim)</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="M2" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>DX file-upload component bound to claim case's Documents page list; virus scan via existing integration connector; max 10 files/25MB enforced client- and server-side.</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>DX file-upload component bound to claim case's Documents page list; virus scan via existing integration connector (see EX-IF1-style pattern); max 10 files/25MB enforced client- and server-side.</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>Policyholder</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>feature:submit-claim-web</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>Sourced</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>Transcript 2026-09-10, 00:14:30; Requirements.xlsx row 22</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>Assumes existing document-storage integration from prior project can be reused as-is.</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t>Does not include mobile app upload (separate story) or OCR/data extraction from uploaded documents.</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="5">
+  <dataValidations count="7">
     <dataValidation sqref="E2:E200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Story,Enabler,Spike"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Functional,Foundation/Overhead"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L2:L200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Highest,High,Medium,Low,Lowest"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"1,2,3,5,8,13,21"</formula1>
+    <dataValidation sqref="M2:M200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"1,2,3,5,8,13"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Low,Medium,High,Complex"</formula1>
     </dataValidation>
-    <dataValidation sqref="S2:S200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="R2:R200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Sourced,Inferred"</formula1>
+    </dataValidation>
+    <dataValidation sqref="V2:V200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Draft,In Review,Approved,Ready for Import"</formula1>
     </dataValidation>
   </dataValidations>
@@ -865,7 +1144,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -907,7 +1186,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
